--- a/jogos_2024-12-16.xlsx
+++ b/jogos_2024-12-16.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.52</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.5</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X8" t="n">
         <v>2.3</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.45</v>
-      </c>
       <c r="Y8" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Z8" t="n">
         <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['8', '64', '69']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['90+6']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45642.4375</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -1564,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>4.52</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="N9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O9" t="n">
         <v>3.5</v>
       </c>
-      <c r="O9" t="n">
-        <v>2.75</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Z9" t="n">
         <v>1.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['8', '64', '69']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45642.4375</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>SCM Gloria Buzău</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>5.84</v>
+        <v>3.18</v>
       </c>
       <c r="N16" t="n">
-        <v>7.48</v>
+        <v>6.71</v>
       </c>
       <c r="O16" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="Q16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="X16" t="n">
-        <v>8.220000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.89</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>3.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['8', '29', '63', '90+8']</t>
+          <t>['5', '21']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['17', '51', '55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.5</v>
+        <v>2.29</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45642.625</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,16 +2578,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="M17" t="n">
-        <v>4.8</v>
+        <v>7.63</v>
       </c>
       <c r="N17" t="n">
-        <v>5.39</v>
+        <v>6.26</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
         <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['27', '89']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45642.625</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SCM Gloria Buzău</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
-        <v>3.18</v>
+        <v>5.84</v>
       </c>
       <c r="N18" t="n">
-        <v>6.71</v>
+        <v>7.48</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['8', '29', '63', '90+8']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['17', '51', '55']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>3.6</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['5', '21']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45642.625</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,16 +2836,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>7.63</v>
+        <v>4.8</v>
       </c>
       <c r="N19" t="n">
-        <v>6.26</v>
+        <v>5.39</v>
       </c>
       <c r="O19" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
         <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X19" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['27', '89']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45642.625</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Kallithea</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>9.26</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="N20" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="O20" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.22</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['50', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['36', '65', '69']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.4</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45642.64583333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kallithea</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9.26</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="O21" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="P21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['50', '90+1']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['36', '65', '69']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45642.64583333334</v>
